--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.158.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.158.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.158.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.158.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y33"/>
+  <dimension ref="A1:Y34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.158.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.158.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0158.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0158.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L105: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 9 6 takenby</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]SCHEDULE OF FEES.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]SCHEDULE OF FEES.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L17: isolated marker/symbol line :: 7</t>
@@ -628,7 +632,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 9 6 takenby</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,14 +666,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”See as to this charge Order 20 of January, 1851,</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”This charge is subject to the restrictions of Order</t>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 9 6 takenby</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -717,21 +721,13 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Pr Ã¦ acipe-for Subpena or other process, entering</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”See as to this charge Order 20 of January, 1851,</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L20: isolated marker/symbol line :: 、</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -762,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -777,11 +773,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: PrÃ¦cipe-for SubpÅ“na or other process, entering</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -832,11 +824,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”One Subpoena only allowed to each County, which</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -883,11 +871,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”See Orders of 1850 as to Interrogatories.</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -986,7 +970,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: Â·</t>
+          <t>L29: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1013,12 +997,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1033,7 +1017,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: Â·</t>
+          <t>L30: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1061,7 +1045,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1099,7 +1083,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1190,7 +1174,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1799,7 +1783,7 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: 0</t>
+          <t>L105: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr"/>
@@ -1830,7 +1814,7 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: ) 6</t>
+          <t>L106: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -1845,6 +1829,37 @@
       <c r="X33" s="1" t="inlineStr"/>
       <c r="Y33" s="1" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr"/>
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" s="1" t="inlineStr"/>
+      <c r="D34" s="1" t="inlineStr"/>
+      <c r="E34" s="1" t="inlineStr"/>
+      <c r="F34" s="1" t="inlineStr"/>
+      <c r="G34" s="1" t="inlineStr"/>
+      <c r="H34" s="1" t="inlineStr"/>
+      <c r="I34" s="1" t="inlineStr"/>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
+      <c r="L34" s="1" t="inlineStr"/>
+      <c r="M34" s="1" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>L107: isolated marker/symbol line :: ) 6</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr"/>
+      <c r="P34" s="1" t="inlineStr"/>
+      <c r="Q34" s="1" t="inlineStr"/>
+      <c r="R34" s="1" t="inlineStr"/>
+      <c r="S34" s="1" t="inlineStr"/>
+      <c r="T34" s="1" t="inlineStr"/>
+      <c r="U34" s="1" t="inlineStr"/>
+      <c r="V34" s="1" t="inlineStr"/>
+      <c r="W34" s="1" t="inlineStr"/>
+      <c r="X34" s="1" t="inlineStr"/>
+      <c r="Y34" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
